--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>0.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -780,13 +780,13 @@
         <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -815,6 +815,7 @@
 Vitsippa
 Kopparödla
 Mindre vattensalamander
+Skogsödla
 Vanlig padda</t>
         </is>
       </c>
@@ -867,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1215,7 +1216,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1323,7 +1324,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1441,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1558,7 @@
         <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1773,7 +1774,7 @@
         <v>44965</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1880,7 +1881,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1988,7 @@
         <v>45420</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2095,7 @@
         <v>45217</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2200,7 +2201,7 @@
         <v>45439</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2306,7 +2307,7 @@
         <v>45988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2412,7 +2413,7 @@
         <v>45106</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2518,7 +2519,7 @@
         <v>44900</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2624,7 +2625,7 @@
         <v>45786</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2730,7 +2731,7 @@
         <v>44980</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2841,7 +2842,7 @@
         <v>44735</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2946,7 +2947,7 @@
         <v>44719</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3056,7 +3057,7 @@
         <v>44621</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3161,7 +3162,7 @@
         <v>45770</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3266,7 +3267,7 @@
         <v>45915</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3371,7 +3372,7 @@
         <v>45917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3476,7 +3477,7 @@
         <v>46029</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3581,7 +3582,7 @@
         <v>46184</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3686,7 +3687,7 @@
         <v>45307</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3796,7 +3797,7 @@
         <v>45509</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3906,7 +3907,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4012,7 @@
         <v>46129</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4121,7 +4122,7 @@
         <v>45258</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4231,7 +4232,7 @@
         <v>44753</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4336,7 +4337,7 @@
         <v>45159</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4441,7 +4442,7 @@
         <v>45774</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4550,7 +4551,7 @@
         <v>46126</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4660,7 +4661,7 @@
         <v>44623</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4733,7 +4734,7 @@
         <v>44691</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4806,7 +4807,7 @@
         <v>44599</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4879,7 +4880,7 @@
         <v>44613</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4952,7 +4953,7 @@
         <v>44879</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5025,7 +5026,7 @@
         <v>44518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5098,7 +5099,7 @@
         <v>44631</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5171,7 +5172,7 @@
         <v>44603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5244,7 +5245,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5317,7 +5318,7 @@
         <v>44482</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5390,7 +5391,7 @@
         <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5463,7 +5464,7 @@
         <v>44508</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5536,7 +5537,7 @@
         <v>44879</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5609,7 +5610,7 @@
         <v>44580</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5682,7 +5683,7 @@
         <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5760,7 +5761,7 @@
         <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5833,7 +5834,7 @@
         <v>44496</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5906,7 +5907,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5979,7 +5980,7 @@
         <v>44679</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6052,7 +6053,7 @@
         <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6125,7 +6126,7 @@
         <v>44888</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6198,7 +6199,7 @@
         <v>44466</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6271,7 +6272,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6344,7 +6345,7 @@
         <v>44524</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6417,7 +6418,7 @@
         <v>44714</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6490,7 +6491,7 @@
         <v>44719</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6568,7 +6569,7 @@
         <v>44552</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6646,7 +6647,7 @@
         <v>45084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6719,7 +6720,7 @@
         <v>45057</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6792,7 +6793,7 @@
         <v>44964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6865,7 +6866,7 @@
         <v>45420</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6938,7 +6939,7 @@
         <v>45259</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7011,7 +7012,7 @@
         <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7084,7 +7085,7 @@
         <v>45769</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7157,7 +7158,7 @@
         <v>44845</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7230,7 +7231,7 @@
         <v>45716</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7303,7 +7304,7 @@
         <v>45434</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7376,7 +7377,7 @@
         <v>44855</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7449,7 +7450,7 @@
         <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7522,7 +7523,7 @@
         <v>45595</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7595,7 +7596,7 @@
         <v>45001</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7668,7 +7669,7 @@
         <v>44942</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7746,7 +7747,7 @@
         <v>45230</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7819,7 +7820,7 @@
         <v>44738</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7892,7 +7893,7 @@
         <v>44637</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7970,7 +7971,7 @@
         <v>45419</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8043,7 +8044,7 @@
         <v>44992</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8116,7 +8117,7 @@
         <v>45006</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8189,7 +8190,7 @@
         <v>45475</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8262,7 +8263,7 @@
         <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8335,7 +8336,7 @@
         <v>44881</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8408,7 +8409,7 @@
         <v>45330</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8486,7 +8487,7 @@
         <v>45306</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8559,7 +8560,7 @@
         <v>45036</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8632,7 +8633,7 @@
         <v>45379</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8705,7 +8706,7 @@
         <v>45099</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8778,7 +8779,7 @@
         <v>44533</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8851,7 +8852,7 @@
         <v>45637</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8924,7 +8925,7 @@
         <v>45068</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8997,7 +8998,7 @@
         <v>45489</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9075,7 +9076,7 @@
         <v>45782</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9148,7 +9149,7 @@
         <v>45789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9221,7 +9222,7 @@
         <v>44700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9299,7 +9300,7 @@
         <v>45888</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9372,7 +9373,7 @@
         <v>44992</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9445,7 +9446,7 @@
         <v>45888</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9518,7 +9519,7 @@
         <v>45712</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9591,7 +9592,7 @@
         <v>45890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9664,7 +9665,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9742,7 +9743,7 @@
         <v>46136</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9815,7 +9816,7 @@
         <v>44701</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9888,7 +9889,7 @@
         <v>45539</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9961,7 +9962,7 @@
         <v>45154</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10034,7 +10035,7 @@
         <v>45159</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10107,7 +10108,7 @@
         <v>45715</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10180,7 +10181,7 @@
         <v>45908</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10253,7 +10254,7 @@
         <v>45757</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10326,7 +10327,7 @@
         <v>44972</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10399,7 +10400,7 @@
         <v>45917</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10472,7 +10473,7 @@
         <v>45070</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10545,7 +10546,7 @@
         <v>45915</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10642,7 +10643,7 @@
         <v>45078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10715,7 +10716,7 @@
         <v>45924</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10788,7 +10789,7 @@
         <v>45925</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10866,7 +10867,7 @@
         <v>45925</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10944,7 +10945,7 @@
         <v>45925</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11022,7 +11023,7 @@
         <v>45931</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11100,7 +11101,7 @@
         <v>45691</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11173,7 +11174,7 @@
         <v>44977</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11246,7 +11247,7 @@
         <v>44967</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11319,7 +11320,7 @@
         <v>45345</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11397,7 +11398,7 @@
         <v>44942</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11475,7 +11476,7 @@
         <v>45937</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11548,7 +11549,7 @@
         <v>45939</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11621,7 +11622,7 @@
         <v>45940</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11699,7 +11700,7 @@
         <v>44823</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11772,7 +11773,7 @@
         <v>45195</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11845,7 +11846,7 @@
         <v>45631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11918,7 +11919,7 @@
         <v>45946</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11991,7 +11992,7 @@
         <v>45953</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12064,7 +12065,7 @@
         <v>45419</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12137,7 +12138,7 @@
         <v>45307</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12215,7 +12216,7 @@
         <v>45954</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12288,7 +12289,7 @@
         <v>45954</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12361,7 +12362,7 @@
         <v>44803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12434,7 +12435,7 @@
         <v>45959</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12512,7 +12513,7 @@
         <v>45953</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12585,7 +12586,7 @@
         <v>45639</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12658,7 +12659,7 @@
         <v>45965</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12731,7 +12732,7 @@
         <v>44977</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12804,7 +12805,7 @@
         <v>45644</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12877,7 +12878,7 @@
         <v>45027</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12955,7 +12956,7 @@
         <v>45782</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13028,7 +13029,7 @@
         <v>45974</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13101,7 +13102,7 @@
         <v>45105</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13174,7 +13175,7 @@
         <v>45981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13247,7 +13248,7 @@
         <v>45610</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13320,7 +13321,7 @@
         <v>45988</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13393,7 +13394,7 @@
         <v>45880</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13466,7 +13467,7 @@
         <v>45040</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13539,7 +13540,7 @@
         <v>45336</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13612,7 +13613,7 @@
         <v>44550</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13685,7 +13686,7 @@
         <v>45713</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13758,7 +13759,7 @@
         <v>45321</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13831,7 +13832,7 @@
         <v>45901</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13904,7 +13905,7 @@
         <v>44953</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13977,7 +13978,7 @@
         <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14050,7 +14051,7 @@
         <v>46008</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14123,7 +14124,7 @@
         <v>45533</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14196,7 +14197,7 @@
         <v>45973</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14269,7 +14270,7 @@
         <v>45840</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14342,7 +14343,7 @@
         <v>45964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14415,7 +14416,7 @@
         <v>44865</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14488,7 +14489,7 @@
         <v>44895</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14561,7 +14562,7 @@
         <v>45757</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14634,7 +14635,7 @@
         <v>45420</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14707,7 +14708,7 @@
         <v>45992</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14780,7 +14781,7 @@
         <v>45078</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14853,7 +14854,7 @@
         <v>46037</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14926,7 +14927,7 @@
         <v>46037</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14999,7 +15000,7 @@
         <v>45776</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15072,7 +15073,7 @@
         <v>46042</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15145,7 +15146,7 @@
         <v>44973</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15223,7 +15224,7 @@
         <v>44973</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15301,7 +15302,7 @@
         <v>45581</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15374,7 +15375,7 @@
         <v>46175</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15447,7 +15448,7 @@
         <v>44489</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15520,7 +15521,7 @@
         <v>46055</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15593,7 +15594,7 @@
         <v>44820</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15666,7 +15667,7 @@
         <v>46053</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15739,7 +15740,7 @@
         <v>44881</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15812,7 +15813,7 @@
         <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15885,7 +15886,7 @@
         <v>44573</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15963,7 +15964,7 @@
         <v>46065</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16036,7 +16037,7 @@
         <v>46065</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16109,7 +16110,7 @@
         <v>46065</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16182,7 +16183,7 @@
         <v>46065</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16260,7 +16261,7 @@
         <v>46064</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16333,7 +16334,7 @@
         <v>46066</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16406,7 +16407,7 @@
         <v>44614</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16479,7 +16480,7 @@
         <v>46182</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16552,7 +16553,7 @@
         <v>44617</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16625,7 +16626,7 @@
         <v>45319</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16698,7 +16699,7 @@
         <v>45175</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16771,7 +16772,7 @@
         <v>45057</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16844,7 +16845,7 @@
         <v>44482</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16917,7 +16918,7 @@
         <v>45201</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16990,7 +16991,7 @@
         <v>46190</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17068,7 +17069,7 @@
         <v>46190</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17146,7 +17147,7 @@
         <v>46190</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17224,7 +17225,7 @@
         <v>44930</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17297,7 +17298,7 @@
         <v>46194</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17370,7 +17371,7 @@
         <v>46097</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17443,7 +17444,7 @@
         <v>46099</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17516,7 +17517,7 @@
         <v>46099</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17589,7 +17590,7 @@
         <v>46099</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17662,7 +17663,7 @@
         <v>45552</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17735,7 +17736,7 @@
         <v>45685</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17808,7 +17809,7 @@
         <v>46107</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17881,7 +17882,7 @@
         <v>46198</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17954,7 +17955,7 @@
         <v>46197</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18027,7 +18028,7 @@
         <v>46202</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18100,7 +18101,7 @@
         <v>45408</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18173,7 +18174,7 @@
         <v>44693</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18246,7 +18247,7 @@
         <v>45335</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18324,7 +18325,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18397,7 +18398,7 @@
         <v>45508</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18470,7 +18471,7 @@
         <v>45314</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18543,7 +18544,7 @@
         <v>46204</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18616,7 +18617,7 @@
         <v>46135</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18689,7 +18690,7 @@
         <v>45426</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18762,7 +18763,7 @@
         <v>45552</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18835,7 +18836,7 @@
         <v>45377</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18908,7 +18909,7 @@
         <v>45539</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18981,7 +18982,7 @@
         <v>45393</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19054,7 +19055,7 @@
         <v>45051</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19127,7 +19128,7 @@
         <v>45425</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19200,7 +19201,7 @@
         <v>45062</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19273,7 +19274,7 @@
         <v>45261</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19346,7 +19347,7 @@
         <v>45555</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19419,7 +19420,7 @@
         <v>44917</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19492,7 +19493,7 @@
         <v>46254</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19565,7 +19566,7 @@
         <v>45327</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19638,7 +19639,7 @@
         <v>45027</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19716,7 +19717,7 @@
         <v>45215</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19789,7 +19790,7 @@
         <v>45769</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19862,7 +19863,7 @@
         <v>46260</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19935,7 +19936,7 @@
         <v>45583</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20008,7 +20009,7 @@
         <v>45379</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20081,7 +20082,7 @@
         <v>45379</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20154,7 +20155,7 @@
         <v>46268</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20227,7 +20228,7 @@
         <v>45229</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20300,7 +20301,7 @@
         <v>45720</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20373,7 +20374,7 @@
         <v>45776</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20451,7 +20452,7 @@
         <v>46273</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20524,7 +20525,7 @@
         <v>46273</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20597,7 +20598,7 @@
         <v>46274</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20670,7 +20671,7 @@
         <v>46274</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20743,7 +20744,7 @@
         <v>45495</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20816,7 +20817,7 @@
         <v>45786</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20889,7 +20890,7 @@
         <v>45789</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20962,7 +20963,7 @@
         <v>45439</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21035,7 +21036,7 @@
         <v>45114</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21108,7 +21109,7 @@
         <v>45552</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21181,7 +21182,7 @@
         <v>45270</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21254,7 +21255,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21327,7 +21328,7 @@
         <v>46272</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21400,7 +21401,7 @@
         <v>45736</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21473,7 +21474,7 @@
         <v>45544</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21546,7 +21547,7 @@
         <v>45775</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21619,7 +21620,7 @@
         <v>45810</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21697,7 +21698,7 @@
         <v>45769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21770,7 +21771,7 @@
         <v>45673</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21843,7 +21844,7 @@
         <v>45030</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21916,7 +21917,7 @@
         <v>44655</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21989,7 +21990,7 @@
         <v>45029</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22062,7 +22063,7 @@
         <v>45077</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22135,7 +22136,7 @@
         <v>44498</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22208,7 +22209,7 @@
         <v>45387</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22281,7 +22282,7 @@
         <v>45992</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22354,7 +22355,7 @@
         <v>46045</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44987</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45420</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>44965</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45439</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45106</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45217</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45917</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45915</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45509</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>46129</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45770</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45307</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44621</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45258</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44719</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45159</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44679</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44466</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44771</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44524</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45230</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45377</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45327</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45229</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44489</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44881</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44482</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45085</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45412</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45040</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44881</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44953</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44865</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44533</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44973</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45736</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45789</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45888</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45890</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>46037</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45070</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>46037</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>46055</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>46053</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45691</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45915</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45420</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46064</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>46065</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>46065</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>46065</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>46066</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>46065</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45924</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45925</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45925</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45925</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45931</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45154</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44714</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45057</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45539</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45581</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>46097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>46099</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>46099</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>46099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45946</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45062</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45810</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46107</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45434</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44895</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45953</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45954</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45954</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45319</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45959</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45006</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45965</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45644</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44977</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45489</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45595</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>46135</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45393</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45782</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>46136</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>44855</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>46008</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>45637</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>45973</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>44972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>45027</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45084</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45426</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45261</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45555</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45782</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45639</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45099</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45953</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45880</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45610</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45769</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>46164</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45840</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45964</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45408</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45769</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45776</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45992</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45335</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45475</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45159</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45720</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45673</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45175</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45379</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>46190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46190</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46190</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>44550</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>46197</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45201</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>46198</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45078</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>45078</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>44614</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>46202</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44573</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>46204</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45345</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>45027</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>44637</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>46254</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>44617</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45583</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45685</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46260</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44719</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45314</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>44700</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45336</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45715</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44738</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45307</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44693</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>46268</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>44845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>46273</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>46273</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>46274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45552</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44992</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>46274</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45215</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46272</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45419</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46182</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45001</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45379</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45379</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44964</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45508</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45057</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44552</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>44977</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45306</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45068</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44992</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>44823</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45757</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45757</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45533</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44942</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45713</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45712</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44942</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45631</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45195</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45776</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45495</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45786</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45789</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45439</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45270</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45114</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45552</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44655</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45030</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45029</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45077</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>44498</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45387</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45992</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>46045</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45327</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44987</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45420</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>44965</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45439</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45106</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45217</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45917</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>45915</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>45509</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>46129</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45770</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45307</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>46029</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>46184</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46197</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>44753</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>44621</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>45258</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44719</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45159</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44679</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44466</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44771</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44524</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45230</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45377</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45327</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44803</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45229</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44489</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44881</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44482</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45085</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45412</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44820</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45040</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45420</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45110</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44881</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45259</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44953</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44865</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45754</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44533</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44973</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45544</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45736</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45330</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45789</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45888</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45888</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45539</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45890</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>46037</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45070</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>46037</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>46042</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>46055</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>46053</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45691</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45915</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>45420</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>46064</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>46065</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>46065</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>46065</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>46066</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>46065</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>45924</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>45925</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45925</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45925</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45931</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45154</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44714</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45057</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45539</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45581</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>46097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>46099</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>46099</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>46099</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45946</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45062</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45810</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>46107</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45434</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44895</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45953</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45954</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45954</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45319</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45959</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45006</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45965</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45644</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44977</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45489</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45988</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45595</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>46135</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45393</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45782</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>46136</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>44855</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>46008</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>45637</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>45973</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         <v>44972</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>45027</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45084</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45716</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45426</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45261</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45555</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45782</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45639</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45099</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45953</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45880</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45610</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45769</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>46164</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45840</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45964</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45408</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>45769</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15227,7 +15227,7 @@
         <v>45776</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45992</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>45335</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>44973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>45475</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>46178</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45159</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45720</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45673</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45175</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>45379</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>46190</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46190</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46190</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>44550</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>46197</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
         <v>45201</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>46198</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45078</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>45078</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>44614</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16858,7 +16858,7 @@
         <v>46202</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16931,7 +16931,7 @@
         <v>44573</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>46204</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>45345</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17160,7 +17160,7 @@
         <v>45027</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>44637</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
         <v>46254</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>44617</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45583</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>45685</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17608,7 +17608,7 @@
         <v>46260</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44701</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44719</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>45314</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>44700</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45336</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45715</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44738</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45307</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44693</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>46268</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>44845</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>46273</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>46273</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>46274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>45552</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44992</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>46274</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45215</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46272</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45419</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46182</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>45001</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>45379</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45379</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44964</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45051</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>45508</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45057</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45036</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>44552</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>44977</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45306</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>45068</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44992</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>44823</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45757</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45757</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45533</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44942</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45713</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45712</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44942</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45631</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45195</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45776</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45495</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45786</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45789</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45439</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45270</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45114</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45552</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44655</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45030</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45029</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45077</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>44498</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45387</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45992</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>46045</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45553</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>44987</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45327</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45926</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44965</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45420</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45217</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45940</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45439</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44719</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45915</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45509</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>44621</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>46129</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45770</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>46029</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46184</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46197</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45258</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>44753</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45159</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44679</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44524</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44714</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>45084</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>44719</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45057</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44964</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45259</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45789</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45434</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45439</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45114</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>46008</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45552</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45973</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44855</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45888</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45888</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45890</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45270</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45412</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44942</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45595</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45001</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>46037</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>46037</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45230</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45754</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46042</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>44637</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44738</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45736</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>46055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45419</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>46053</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45924</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45925</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44992</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45925</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45775</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45931</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46065</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46065</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>46065</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>46065</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45475</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>46066</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45939</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45104</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45330</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>45946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45810</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45953</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45954</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45954</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45959</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45036</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45306</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>46099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>46099</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46099</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45379</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45974</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45099</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45981</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44533</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45637</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45068</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45988</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44700</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46135</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44992</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45712</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45085</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>44701</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45393</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45539</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45154</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45159</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45769</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45489</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45757</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44972</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45782</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45070</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45078</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>46136</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45691</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>44977</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44967</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45345</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44942</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44823</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45195</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45631</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45419</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45307</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44803</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45953</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45639</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>44977</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45782</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45644</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45027</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45673</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>45880</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45105</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>46164</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45610</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>45992</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45776</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45040</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>46175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45789</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>45336</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44550</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45713</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45321</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>46190</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46190</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>46190</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45533</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>46198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46197</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46202</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44865</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>46204</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45757</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45420</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45078</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44973</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45581</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44489</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>46260</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44881</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44573</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44614</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>46268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>46273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46273</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44617</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45319</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>46274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45175</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45057</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44482</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45201</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>44930</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>46272</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45685</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45408</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>44693</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45335</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45508</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45314</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>46182</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45426</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45552</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45377</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45539</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45051</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>46107</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46294</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>46254</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45140</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45425</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45062</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45261</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45555</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45327</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45027</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45215</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45583</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45379</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45379</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45229</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45720</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45776</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45495</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45786</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45030</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44655</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45077</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44498</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45387</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>46045</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45553</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>44987</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45327</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45926</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44965</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45420</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45217</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45940</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45439</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44719</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>45915</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45509</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>44621</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>46129</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>45774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45770</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>46029</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46184</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>46197</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>45307</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>45258</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>44753</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45159</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44679</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44524</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44714</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44552</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>45084</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>44719</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45716</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45057</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>44964</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45420</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45259</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45110</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>45789</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45434</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45439</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45114</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>46008</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45552</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45973</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44855</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45888</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45888</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45890</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45270</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45412</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>44942</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45595</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45001</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>46037</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>46037</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45230</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45754</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>46042</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>44637</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44738</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45736</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45917</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45915</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45544</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>46055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45419</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>46053</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45924</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45925</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>44992</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45925</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9868,7 +9868,7 @@
         <v>45925</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45775</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45006</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>45931</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>46065</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>46065</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>46065</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>46065</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45475</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>46066</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45939</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45104</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44881</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45330</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>45946</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45810</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>45953</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45954</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45954</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45959</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45036</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45306</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>46097</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>46099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>46099</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>46099</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>45379</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45974</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45099</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45981</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44533</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45637</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45068</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45988</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44700</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>46135</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44992</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45712</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45085</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>44701</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45393</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45539</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45154</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45159</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45769</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45489</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45757</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44972</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45782</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45070</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45078</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>46136</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45691</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>44977</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>44967</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45345</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>44942</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44823</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45195</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45631</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45419</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45307</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44803</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45953</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45639</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>44977</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45782</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45644</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45027</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15262,7 +15262,7 @@
         <v>45673</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15335,7 +15335,7 @@
         <v>45880</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>45105</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15481,7 +15481,7 @@
         <v>45901</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
         <v>46164</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45840</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45964</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45610</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>45992</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45776</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45040</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>46175</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45789</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>45336</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>44550</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45713</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45321</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>46190</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46190</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16732,7 +16732,7 @@
         <v>46190</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44953</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45533</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>46198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46197</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46202</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>44865</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>44895</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>46204</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45757</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45420</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45078</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44973</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45581</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44489</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44820</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>46260</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44881</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44573</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44614</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>46268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>46273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46273</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44617</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45319</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>46274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45175</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45057</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44482</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45201</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>44930</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>46272</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45552</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45685</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45408</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>44693</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45335</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45508</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45314</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>46182</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45426</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45552</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45377</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45539</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45051</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>46107</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46294</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>46254</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45140</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45425</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45062</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45261</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45555</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45327</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45027</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45215</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45769</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45583</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45379</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45379</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45229</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45720</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45776</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45495</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45786</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45030</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44655</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45029</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45077</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44498</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45387</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45992</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>46045</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45926</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45420</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>44965</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45439</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45106</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45786</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45217</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45307</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45159</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44621</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46129</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45258</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45770</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>46029</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>46184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>46197</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44580</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44679</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44482</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44771</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45306</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45412</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45419</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45261</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>45040</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45555</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45230</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45099</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44917</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45377</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45104</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45327</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45610</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44992</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>44489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45420</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44823</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45229</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45757</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45757</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45110</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45408</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45533</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44942</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44881</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45259</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45789</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45769</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45888</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45713</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44865</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44533</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45888</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45335</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45890</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44942</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45631</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45195</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45475</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45159</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45720</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45175</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44930</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45495</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45915</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45379</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45917</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45786</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45691</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45420</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45924</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45789</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45925</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45925</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45925</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45439</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45270</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45114</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45552</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44550</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45201</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45754</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45154</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44714</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45057</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45736</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45078</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45539</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45345</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45027</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45775</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45062</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45939</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45434</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44895</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45946</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45425</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45319</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45006</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44617</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45583</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45953</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45954</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45954</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44967</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45685</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45644</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44701</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44977</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>44719</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45769</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45314</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44700</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45595</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45336</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45715</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44738</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45307</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44693</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44855</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45673</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45637</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45552</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45321</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44972</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44992</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45981</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45027</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>46097</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>46099</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46099</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>46099</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45215</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45769</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45716</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45988</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45426</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45552</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45105</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45419</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>46008</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45489</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>46135</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45001</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45379</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45379</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>44964</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45393</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45782</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>46136</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>46037</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>46037</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45051</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45508</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45057</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44552</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>44977</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>46055</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>46053</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>46064</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>46065</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46065</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>46065</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>46066</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>46065</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45782</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45639</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45953</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45880</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45901</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>46164</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45840</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45776</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46175</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>46190</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>46190</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46190</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>46197</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>46198</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>46202</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>46204</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>46268</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>46273</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>46273</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>46274</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>46274</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46272</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46182</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>46294</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45140</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>46300</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>46107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46254</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>46302</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>46260</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>46300</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>46302</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44655</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45030</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45029</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45077</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44498</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45387</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45992</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46045</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>45925</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45926</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45420</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>44965</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45439</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45106</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45786</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45217</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>45307</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44719</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>45159</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45915</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>44753</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44621</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>46129</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>45258</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45770</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>45509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>46029</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>46184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>46197</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44580</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44700</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44679</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44550</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44881</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44482</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44771</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45306</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44820</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45412</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45419</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45261</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>45040</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45555</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45230</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45099</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44917</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45377</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45104</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45327</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45610</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44803</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44992</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>44489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45420</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44823</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45229</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45757</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45757</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45110</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45408</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45533</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44942</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44881</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45259</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44953</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45789</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45769</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45888</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45713</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44865</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44533</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45888</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45335</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45890</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44942</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45330</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45631</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45195</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45070</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>44973</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45475</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45159</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45776</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45720</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45175</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44930</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45495</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45915</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45379</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45917</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45786</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45691</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45420</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45924</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45789</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45925</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45925</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45925</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45439</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45270</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45114</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45552</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44550</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45201</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45754</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45154</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44714</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45057</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>45736</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45078</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45078</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44573</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45539</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45345</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45027</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45775</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45062</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>44637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>45939</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45434</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44895</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45946</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45425</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45319</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45006</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44617</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45583</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45953</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45954</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45954</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>45959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44967</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45685</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45644</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44701</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45965</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>44977</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>44719</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45769</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>45314</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>44700</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45595</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45974</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45336</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45715</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>44738</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45307</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44693</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44855</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45673</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45637</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45552</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45321</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44972</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44992</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45981</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45027</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>46097</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>46099</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46099</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>46099</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45215</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45769</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45716</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45988</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45426</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45552</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45105</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45419</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>46008</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45489</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>46135</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45001</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45379</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45379</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>44964</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>45393</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45782</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>46136</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>46037</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>46037</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>46042</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45051</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45508</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45057</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45036</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>44552</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>44977</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>46055</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>46053</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>46064</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>46065</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46065</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>46065</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>46066</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>46065</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45782</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45639</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45953</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45880</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45901</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>46164</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45840</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45964</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45776</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45992</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>46175</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>46178</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>46190</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>46190</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46190</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>46197</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20636,7 +20636,7 @@
         <v>46198</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>46202</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>46204</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>46268</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20928,7 +20928,7 @@
         <v>46273</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>46273</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>46274</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>46274</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>46272</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46182</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>46294</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45140</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>46300</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>46107</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46254</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>46302</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>46260</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>46300</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>46302</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44655</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45030</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45029</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45077</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>44498</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45387</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45992</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>46045</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44965</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45420</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45217</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45439</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44719</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45770</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45917</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>46029</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45509</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>46129</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45258</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45159</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45774</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44508</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44879</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44580</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44496</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44679</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44888</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44771</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45716</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44714</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45057</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>44552</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45084</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45420</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45259</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45434</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44855</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45412</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44942</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45001</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45595</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>44738</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>44637</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45419</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>45475</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44881</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>45330</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45006</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>45306</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45379</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45099</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>45637</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45068</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>45489</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45789</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45888</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45888</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>45890</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>46136</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44700</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44992</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44701</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45159</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45715</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45757</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45924</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45925</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45925</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44972</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45925</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45931</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45937</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>45939</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45953</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45639</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45946</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44977</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45782</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44967</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>45345</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>44942</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45954</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45965</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45880</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44823</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45631</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45974</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45419</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45307</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45981</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44977</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45644</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45901</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45027</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>46164</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45988</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45840</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45105</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45610</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45040</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45776</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45336</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44550</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>46175</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45321</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46037</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>46178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>46042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>44953</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>46055</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>46053</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>46065</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>46065</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>46065</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>46065</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>46064</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>46066</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44865</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45757</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45420</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>46190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>46190</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>46190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44973</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>46099</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>46099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>46099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45581</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44489</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44820</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44573</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>46198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>46202</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44614</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>46204</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44617</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>46135</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45319</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45175</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45057</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45201</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45393</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>44930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45552</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45685</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45408</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44693</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>45335</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>46273</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>46273</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>46274</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45508</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>46274</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45314</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45426</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45552</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45377</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45539</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>46272</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45051</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45425</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45062</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45555</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>44917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45327</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45027</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45215</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>46182</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45769</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45583</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45379</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45379</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46107</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46294</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>46254</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45140</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45229</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46300</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45720</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45776</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45495</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>46300</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45786</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46302</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>45789</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45439</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45114</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45552</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45270</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>46302</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45736</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45544</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45775</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45810</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45673</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45030</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44655</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45029</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45077</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>44498</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45387</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45992</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>46045</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>44987</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>45327</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>45925</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>45821</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44965</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>45420</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>45217</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45940</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>45439</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>45106</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44900</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44980</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>44735</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>44719</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>44621</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>45770</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>45917</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>46029</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46184</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45509</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>46197</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>46129</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45307</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>45258</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>44753</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>45159</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45774</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44623</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44691</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44599</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44879</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44631</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44508</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44879</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44580</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44700</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44550</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44496</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44517</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>44679</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44888</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44771</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44524</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44845</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45716</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44714</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44719</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45057</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>44552</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45084</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>44964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45420</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45259</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45110</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45769</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45434</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44855</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45412</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44942</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45001</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45595</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45230</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>44738</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>44637</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45419</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>45475</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>44881</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>45330</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45104</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45006</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>45036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>45306</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45379</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45099</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44533</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>45637</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45068</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>45489</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>45789</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45888</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45888</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>45890</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>46136</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44700</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44992</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>44701</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45159</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45715</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45757</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45924</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45925</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45925</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>44972</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45925</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>45070</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>45078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>45931</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>45937</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>45939</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>45953</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11212,7 +11212,7 @@
         <v>45639</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45946</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>45691</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44977</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45782</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45953</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44967</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11723,7 +11723,7 @@
         <v>45345</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>44942</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45954</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45965</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>45880</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>44823</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45195</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45631</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45974</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45419</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45307</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>45981</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44977</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>45644</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45901</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45027</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13135,7 +13135,7 @@
         <v>46164</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45988</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45840</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45964</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45105</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>45610</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46008</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45040</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45776</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>45336</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>44550</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>46175</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>45713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>45321</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46037</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>46037</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>46178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>46042</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>44953</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>46055</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>46053</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>46065</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>46065</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>46065</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>46065</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>46064</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>46066</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44865</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44895</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45757</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45420</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45078</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>46190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>46190</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>46190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>44973</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46097</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>44973</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>46099</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>46099</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>46099</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>45581</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>44489</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>44820</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44881</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44573</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>46198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>46197</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>46202</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>44614</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>46204</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44617</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>46135</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45319</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>45175</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45057</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45201</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45393</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>44930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45552</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>45685</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45408</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44693</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>45335</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>46273</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>46273</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>46274</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45508</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>46274</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45314</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45426</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45552</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45377</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45539</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>46272</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45051</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45425</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45062</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45555</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>44917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45327</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45027</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45215</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>46182</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45769</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45583</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45379</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45379</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46107</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46294</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>46254</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45140</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45229</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46300</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45720</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45776</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>45495</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>46300</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>45786</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>46302</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>45789</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45439</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45114</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45552</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45270</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>46302</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45736</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45544</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45775</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45810</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>46268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45769</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45673</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45030</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>44655</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45029</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45077</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>44498</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45387</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45992</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>46045</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>46311</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>45327</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44987</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45821</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45420</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44965</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>44900</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45940</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45439</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45217</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>44980</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44735</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>46029</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46197</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44719</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45159</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45509</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45774</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>46129</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45770</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45307</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>44753</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45258</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>46126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44691</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44599</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>44613</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>44879</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>44518</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>44631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44679</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44524</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>45789</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45888</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45888</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>45230</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45377</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45327</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45379</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45379</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44964</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44881</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45901</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45840</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>45964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>45925</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45412</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45925</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45925</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45419</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45776</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45051</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45508</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45992</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>46175</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45057</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45937</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45939</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45040</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45946</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>46178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45420</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45068</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45959</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>46190</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>46190</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44823</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>46190</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45757</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45974</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45533</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44942</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>46198</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>46202</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45981</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45713</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45110</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>46204</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45712</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44942</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45631</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45988</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>44881</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45776</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45259</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>46008</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45495</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45973</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45786</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>44953</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45789</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>45439</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45270</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45114</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>46037</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>46037</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45754</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45544</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45736</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>46055</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>46053</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45775</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44865</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>44533</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>46064</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>46065</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>46065</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46065</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46066</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46065</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>46294</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45140</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46300</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>46107</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46254</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>46097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46099</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46099</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45330</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45769</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>46260</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>46300</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>46302</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45539</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45673</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>44930</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>46135</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45393</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45782</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45691</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>46136</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>46314</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45420</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>46302</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>46314</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46314</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>46316</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>46314</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>46272</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>46273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>46273</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45154</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44714</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45057</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>46316</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>46274</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>46274</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45539</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45581</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45062</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45434</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44895</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45782</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45425</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45639</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45319</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45880</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45644</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44977</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45595</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44855</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45637</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44972</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45027</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45769</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45084</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45716</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45426</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45555</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44917</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45104</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45610</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45408</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45769</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45335</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44973</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45475</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45159</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45720</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45175</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45379</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44550</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45201</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45078</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45078</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44573</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45345</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45027</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44637</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44617</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45583</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45685</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>44719</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45314</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44700</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45336</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45715</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44738</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45307</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44693</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44845</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45321</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>44992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45215</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45552</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45105</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45419</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44655</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45077</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44498</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45387</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45992</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>46045</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>

--- a/Översikt TRANÅS.xlsx
+++ b/Översikt TRANÅS.xlsx
@@ -601,7 +601,7 @@
         <v>45433</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46077</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>46133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>45162</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>46311</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>45925</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>45553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>45327</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>44987</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45821</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>45926</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>45420</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44965</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>44900</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45940</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45988</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>45439</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>45106</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>45217</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>44980</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44735</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>46029</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>45917</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>45915</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46197</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>44719</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45159</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45509</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45774</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>46129</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>45770</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45307</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>44753</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45258</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>46126</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>44623</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44691</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>44599</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>44613</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>44879</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>44518</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>44631</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44508</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>44879</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44700</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44550</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44517</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>44679</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44587</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44888</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44771</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44524</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>45789</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45888</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45888</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>45230</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45377</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>45327</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45001</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45229</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45379</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45379</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44964</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44881</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45901</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>45917</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45840</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>44820</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>45964</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>45925</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>45412</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45925</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45925</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45419</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>45776</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45931</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45051</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45508</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45992</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>46175</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45057</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45036</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>44552</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>45937</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45939</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45040</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>45946</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>46178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45420</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45068</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45959</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>45965</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10347,7 +10347,7 @@
         <v>46190</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>46190</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44823</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>46190</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45757</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>45757</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>45974</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>45533</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44942</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>46198</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>46202</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>45981</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45713</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45110</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>46204</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45712</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44942</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>45631</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>45195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45988</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>44881</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45776</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45259</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>46008</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45495</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>45973</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45786</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>44953</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45789</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>45439</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45270</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45114</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45552</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>46037</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>46037</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>46042</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45754</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45544</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45736</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>46182</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>46055</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>46053</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45775</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44865</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>44533</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>46064</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>46065</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>46065</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46065</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46066</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46065</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>46294</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44973</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45140</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46300</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>46107</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46254</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>46097</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>46099</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46099</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46099</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45330</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45769</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>46260</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>46300</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>46302</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45539</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45673</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45070</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45489</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>44930</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>46135</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45393</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45782</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45691</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>46136</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>46314</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16242,7 +16242,7 @@
         <v>45420</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         <v>46302</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>46314</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46314</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>46316</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>46314</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>46272</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>46273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>46273</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45154</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44714</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45057</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>46316</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>46274</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>46274</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45539</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45581</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45062</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45434</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44895</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45782</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45425</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45639</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         <v>45953</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17994,7 +17994,7 @@
         <v>45319</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45880</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>44967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45644</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>44977</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45595</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>44855</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45637</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44972</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>45027</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>45769</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45084</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45716</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45426</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45555</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45099</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44917</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45104</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45610</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45408</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45769</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45335</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>44973</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45475</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45159</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45720</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20053,7 +20053,7 @@
         <v>45175</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         <v>45379</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44550</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>45201</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45078</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45078</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44573</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45345</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45027</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44637</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44617</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45583</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45685</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>44719</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45314</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44700</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45336</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45715</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>44738</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45307</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44693</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>44845</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>45321</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>44992</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45215</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45552</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45105</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45419</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>44655</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45030</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45077</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>44498</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45387</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45992</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>46045</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
